--- a/Current TAPPs/Solution_Q-ICP-MS_TAPP_v34.xlsx
+++ b/Current TAPPs/Solution_Q-ICP-MS_TAPP_v34.xlsx
@@ -547,7 +547,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Description / Purpose</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
